--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487015_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487015_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1782</v>
+        <v>7.7671</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8535</v>
+        <v>5.4424</v>
       </c>
       <c r="F2" t="n">
         <v>2.3247</v>
@@ -610,10 +610,10 @@
         <v>3.0801</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2979</v>
+        <v>-0.709</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7518</v>
+        <v>-0.1629</v>
       </c>
       <c r="U2" t="n">
         <v>-0.5461</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6924</v>
+        <v>3.3934</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6336</v>
+        <v>3.4452</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0588</v>
+        <v>-0.0519</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6136</v>
+        <v>-2.0003</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4056</v>
+        <v>0.068</v>
       </c>
       <c r="I3" t="n">
-        <v>0.208</v>
+        <v>-2.0683</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5732</v>
+        <v>1.2346</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9023</v>
+        <v>1.5641</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6709000000000001</v>
+        <v>-0.3295</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9596</v>
+        <v>-3.2349</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4967</v>
+        <v>-1.4961</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4629</v>
+        <v>-1.7388</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6427</v>
+        <v>2.4641</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6694</v>
+        <v>3.4908</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5449</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>3.196</v>
+        <v>-0.2986</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3489</v>
+        <v>-0.3078</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1088</v>
+        <v>3.5359</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.1088</v>
+        <v>3.5359</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3547</v>
+        <v>3.1606</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2287</v>
+        <v>1.3983</v>
       </c>
       <c r="F4" t="n">
-        <v>0.126</v>
+        <v>1.7623</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.0003</v>
+        <v>0.6136</v>
       </c>
       <c r="H4" t="n">
-        <v>0.068</v>
+        <v>0.4056</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0683</v>
+        <v>0.208</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2346</v>
+        <v>1.5732</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5641</v>
+        <v>0.9023</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.3295</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2349</v>
+        <v>-0.9596</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4961</v>
+        <v>-0.4967</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7388</v>
+        <v>-0.4629</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4641</v>
+        <v>1.6427</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>3.4908</v>
+        <v>2.6694</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.645</v>
+        <v>1.0131</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5151</v>
+        <v>0.9606</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.13</v>
+        <v>0.0524</v>
       </c>
       <c r="V4" t="n">
-        <v>3.5359</v>
+        <v>-0.1088</v>
       </c>
       <c r="W4" t="n">
-        <v>3.5359</v>
+        <v>-0.1088</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.8578</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2404</v>
+        <v>0.4531</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3158</v>
+        <v>0.4048</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0885</v>
@@ -844,13 +844,13 @@
         <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2386</v>
+        <v>-0.4562</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8563</v>
+        <v>-0.1628</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3823</v>
+        <v>-0.2934</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2402</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8974</v>
+        <v>-1.0177</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5581</v>
+        <v>1.3489</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4555</v>
+        <v>-2.3665</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9143</v>
@@ -922,13 +922,13 @@
         <v>0.2053</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.057</v>
+        <v>-0.1773</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3021</v>
+        <v>0.0929</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3591</v>
+        <v>-0.2702</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1314</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8851</v>
+        <v>-2.1493</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9684</v>
+        <v>-0.9229000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8535</v>
+        <v>-1.2264</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.4874</v>
+        <v>-1.8594</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.0927</v>
+        <v>1.2691</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3947</v>
+        <v>-3.1285</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3713</v>
+        <v>-0.4423</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1806</v>
+        <v>1.5972</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5518</v>
+        <v>-2.0396</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.8586</v>
+        <v>-1.4171</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9121</v>
+        <v>-0.3281</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.9465</v>
+        <v>-1.089</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4107</v>
+        <v>2.2588</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4641</v>
+        <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1916</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.472</v>
+        <v>-0.4806</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2803</v>
+        <v>-0.3001</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1786</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9268</v>
+        <v>-3.2589</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7598</v>
+        <v>-0.2868</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1671</v>
+        <v>-2.9721</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8594</v>
+        <v>-3.4874</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2691</v>
+        <v>-2.0927</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.1285</v>
+        <v>-1.3947</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4423</v>
+        <v>0.3713</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5972</v>
+        <v>-1.1806</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0396</v>
+        <v>1.5518</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4171</v>
+        <v>-3.8586</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3281</v>
+        <v>-0.9121</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.089</v>
+        <v>-2.9465</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2588</v>
+        <v>0.4107</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>2.2588</v>
+        <v>2.4641</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5582</v>
+        <v>-0.1822</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3174</v>
+        <v>0.2167</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2408</v>
+        <v>-0.3989</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7679</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7679</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.6963</v>
+        <v>-3.9066</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4933</v>
+        <v>-2.9703</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2031</v>
+        <v>-0.9363</v>
       </c>
       <c r="G9" t="n">
         <v>-5.0795</v>
@@ -1156,13 +1156,13 @@
         <v>2.8748</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7052</v>
+        <v>-0.9154</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8177</v>
+        <v>-0.2947</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8875</v>
+        <v>-0.6207</v>
       </c>
       <c r="V9" t="n">
         <v>0.2402</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.0084</v>
+        <v>-5.6304</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8619</v>
+        <v>-3.6914</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1465</v>
+        <v>-1.939</v>
       </c>
       <c r="G10" t="n">
         <v>-4.1591</v>
@@ -1234,13 +1234,13 @@
         <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8575</v>
+        <v>-0.4795</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.159</v>
+        <v>0.0115</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6985</v>
+        <v>-0.491</v>
       </c>
       <c r="V10" t="n">
         <v>0.2402</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.113300000000001</v>
+        <v>-0.7839999999999989</v>
       </c>
       <c r="E11" t="n">
-        <v>3.886900000000001</v>
+        <v>4.216499999999999</v>
       </c>
       <c r="F11" t="n">
         <v>-5.000400000000001</v>
@@ -1279,7 +1279,7 @@
         <v>-16.4453</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9734000000000004</v>
+        <v>0.9734000000000002</v>
       </c>
       <c r="I11" t="n">
         <v>-17.4185</v>
@@ -1297,7 +1297,7 @@
         <v>-19.0408</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.242900000000001</v>
+        <v>-5.242899999999999</v>
       </c>
       <c r="O11" t="n">
         <v>-13.7978</v>
@@ -1312,13 +1312,13 @@
         <v>20.5341</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.6229</v>
+        <v>-3.2936</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4471999999999996</v>
+        <v>-0.1179</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.1757</v>
+        <v>-3.1758</v>
       </c>
       <c r="V11" t="n">
         <v>7.661199999999999</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. SALO BLAYA</t>
+          <t>E. MARTINEZ PRETEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.9832</v>
+        <v>3.5316</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1489</v>
+        <v>2.3077</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1657</v>
+        <v>1.2239</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4005</v>
+        <v>4.8321</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4242</v>
+        <v>-0.4222</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9762999999999999</v>
+        <v>5.2543</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5447</v>
+        <v>4.728</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7553</v>
+        <v>0.545</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7893</v>
+        <v>4.183</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1441</v>
+        <v>0.104</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3311</v>
+        <v>-0.9673</v>
       </c>
       <c r="O12" t="n">
-        <v>0.187</v>
+        <v>1.0713</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.8214</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0267</v>
+        <v>-4.3122</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2053</v>
+        <v>1.6427</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5827</v>
+        <v>-0.399</v>
       </c>
       <c r="T12" t="n">
-        <v>1.631</v>
+        <v>-0.1164</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9517</v>
+        <v>-0.2826</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1786</v>
+        <v>1.7679</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.0082</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8815</v>
+        <v>3.0018</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4333</v>
+        <v>4.6425</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5518</v>
+        <v>-1.6408</v>
       </c>
       <c r="G13" t="n">
         <v>6.31</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0979</v>
+        <v>0.0224</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1513</v>
+        <v>0.0579</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0533</v>
+        <v>-0.0356</v>
       </c>
       <c r="V13" t="n">
         <v>-3.5359</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. MARTINEZ PRETEL</t>
+          <t>A. LLORCA CASTILLO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4436</v>
+        <v>2.3233</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5754</v>
+        <v>1.792</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8682</v>
+        <v>0.5313</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8321</v>
+        <v>6.7682</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4222</v>
+        <v>1.1744</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2543</v>
+        <v>5.5938</v>
       </c>
       <c r="J14" t="n">
-        <v>4.728</v>
+        <v>6.8327</v>
       </c>
       <c r="K14" t="n">
-        <v>0.545</v>
+        <v>2.0313</v>
       </c>
       <c r="L14" t="n">
-        <v>4.183</v>
+        <v>4.8014</v>
       </c>
       <c r="M14" t="n">
-        <v>0.104</v>
+        <v>-0.0645</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9673</v>
+        <v>-0.8569</v>
       </c>
       <c r="O14" t="n">
-        <v>1.0713</v>
+        <v>0.7924</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.6694</v>
+        <v>-4.5175</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.3122</v>
+        <v>-5.3389</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4869</v>
+        <v>0.0727</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8486</v>
+        <v>0.2982</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6383</v>
+        <v>-0.2255</v>
       </c>
       <c r="V14" t="n">
-        <v>1.7679</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2402</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LLORCA CASTILLO</t>
+          <t>P. SALO BLAYA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1151</v>
+        <v>1.5222</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8505</v>
+        <v>2.1029</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2646</v>
+        <v>-0.5807</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7682</v>
+        <v>2.4005</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1744</v>
+        <v>1.4242</v>
       </c>
       <c r="I15" t="n">
-        <v>5.5938</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>6.8327</v>
+        <v>2.5447</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0313</v>
+        <v>1.7553</v>
       </c>
       <c r="L15" t="n">
-        <v>4.8014</v>
+        <v>0.7893</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0645</v>
+        <v>-0.1441</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8569</v>
+        <v>-0.3311</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7924</v>
+        <v>0.187</v>
       </c>
       <c r="P15" t="n">
-        <v>-4.5175</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.3389</v>
+        <v>-1.0267</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1355</v>
+        <v>1.1217</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6433</v>
+        <v>0.5849</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4923</v>
+        <v>0.5367</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.104</v>
+        <v>1.4928</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7356</v>
+        <v>3.154</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6316</v>
+        <v>-1.6612</v>
       </c>
       <c r="G16" t="n">
         <v>1.9808</v>
@@ -1702,13 +1702,13 @@
         <v>0.8214</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5072</v>
+        <v>0.896</v>
       </c>
       <c r="T16" t="n">
-        <v>0.12</v>
+        <v>0.5384</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3873</v>
+        <v>0.3576</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0964</v>
+        <v>-0.5765</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2523</v>
+        <v>-0.9845</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3488</v>
+        <v>0.408</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7063</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0081</v>
+        <v>0.3352</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1971</v>
+        <v>0.4649</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.189</v>
+        <v>-0.1297</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. KNOWLES</t>
+          <t>E. MOURE COLOMBO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1882</v>
+        <v>-0.8398</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6183999999999999</v>
+        <v>0.5183</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4302</v>
+        <v>-1.3581</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1474</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.5291</v>
+        <v>0.4022</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3817</v>
+        <v>-0.3288</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3304</v>
+        <v>0.1968</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.1986</v>
+        <v>0.0389</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8682</v>
+        <v>0.1579</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8171</v>
+        <v>-0.1234</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3305</v>
+        <v>0.3632</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5134</v>
+        <v>-0.4866</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2321</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4374</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0762</v>
+        <v>0.2654</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3752</v>
+        <v>0.3215</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.299</v>
+        <v>-0.0561</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3491</v>
+        <v>-1.1786</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.4579</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1088</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. OKENCHI</t>
+          <t>D. KNOWLES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9824000000000001</v>
+        <v>-0.8925</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1577</v>
+        <v>-1.5599</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1753</v>
+        <v>0.6673</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3616</v>
+        <v>-2.1474</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4379</v>
+        <v>-3.5291</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.07630000000000001</v>
+        <v>1.3817</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0589</v>
+        <v>-1.3304</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0195</v>
+        <v>-2.1986</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0395</v>
+        <v>0.8682</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3027</v>
+        <v>-0.8171</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4184</v>
+        <v>-1.3305</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1157</v>
+        <v>0.5134</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2053</v>
+        <v>1.4374</v>
       </c>
       <c r="S19" t="n">
-        <v>0.504</v>
+        <v>0.372</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8368</v>
+        <v>0.4338</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3328</v>
+        <v>-0.0618</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.4579</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. MOURE COLOMBO</t>
+          <t>O. OKENCHI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3315</v>
+        <v>-1.3712</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2045</v>
+        <v>-1.5761</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.536</v>
+        <v>0.2049</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.3616</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4022</v>
+        <v>0.4379</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3288</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1968</v>
+        <v>0.0589</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0389</v>
+        <v>0.0195</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1579</v>
+        <v>0.0395</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1234</v>
+        <v>0.3027</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3632</v>
+        <v>0.4184</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4866</v>
+        <v>-0.1157</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2262</v>
+        <v>0.1153</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0077</v>
+        <v>0.4184</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.234</v>
+        <v>-0.3031</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0036</v>
+        <v>-2.3157</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0856</v>
+        <v>-0.1902</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.918</v>
+        <v>-2.1255</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9734</v>
@@ -2092,13 +2092,13 @@
         <v>0.4107</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0047</v>
+        <v>0.6926</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5075</v>
+        <v>0.4029</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4972</v>
+        <v>0.2897</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4189</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.0049</v>
+        <v>-4.7626</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.834</v>
+        <v>-5.2064</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.4438</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4541</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1134</v>
+        <v>0.1289</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8563</v>
+        <v>-0.2287</v>
       </c>
       <c r="U22" t="n">
-        <v>0.743</v>
+        <v>0.3576</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5893</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.1132</v>
+        <v>1.113400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>5.000200000000001</v>
+        <v>5.000299999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8869</v>
+        <v>-3.887100000000001</v>
       </c>
       <c r="G23" t="n">
         <v>16.4454</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9732000000000003</v>
+        <v>-0.9731999999999998</v>
       </c>
       <c r="I23" t="n">
         <v>17.4185</v>
@@ -2248,13 +2248,13 @@
         <v>9.240399999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>3.623</v>
+        <v>3.6232</v>
       </c>
       <c r="T23" t="n">
         <v>3.1758</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4470999999999998</v>
+        <v>0.4471999999999998</v>
       </c>
       <c r="V23" t="n">
         <v>-7.6611</v>
